--- a/laporan_padel_dki_jakarta_2026-09-18.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-18.xlsx
@@ -1381,16 +1381,16 @@
         <v>85</v>
       </c>
       <c r="D31" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.093.000</t>
+          <t>Rp3.222.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1536,16 +1536,16 @@
         <v>64</v>
       </c>
       <c r="D36" t="n">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>42.2%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp5.550.000</t>
+          <t>Rp5.890.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -2032,16 +2032,16 @@
         <v>60</v>
       </c>
       <c r="D52" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp484.000</t>
+          <t>Rp592.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2187,16 +2187,16 @@
         <v>32</v>
       </c>
       <c r="D57" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>28.1%</t>
+          <t>40.6%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp2.225.000</t>
+          <t>Rp3.225.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>144</v>
       </c>
       <c r="D59" t="n">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp2.493.000</t>
+          <t>Rp2.293.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>68</v>
       </c>
       <c r="D61" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>36.8%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp3.810.000</t>
+          <t>Rp4.010.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2528,16 +2528,16 @@
         <v>176</v>
       </c>
       <c r="D68" t="n">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp2.988.000</t>
+          <t>Rp3.237.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -3540,16 +3540,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp5.134.000</t>
+          <t>Rp5.834.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3695,16 +3695,16 @@
         <v>64</v>
       </c>
       <c r="D9" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp3.225.000</t>
+          <t>Rp3.425.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3850,16 +3850,16 @@
         <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp6.350.000</t>
+          <t>Rp6.575.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3974,16 +3974,16 @@
         <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>23.1%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp6.885.000</t>
+          <t>Rp7.695.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4253,16 +4253,16 @@
         <v>17</v>
       </c>
       <c r="D27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp80.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4284,16 +4284,16 @@
         <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp7.871.000</t>
+          <t>Rp8.469.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4315,16 +4315,16 @@
         <v>180</v>
       </c>
       <c r="D29" t="n">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp19.120.000</t>
+          <t>Rp19.470.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -5307,16 +5307,16 @@
         <v>124</v>
       </c>
       <c r="D61" t="n">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>6.5%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp960.000</t>
+          <t>Rp1.060.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -5462,16 +5462,16 @@
         <v>90</v>
       </c>
       <c r="D66" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>32.2%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Rp10.250.000</t>
+          <t>Rp10.500.000</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
@@ -5493,16 +5493,16 @@
         <v>102</v>
       </c>
       <c r="D67" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>27.5%</t>
+          <t>25.5%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp7.866.000</t>
+          <t>Rp7.272.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>144</v>
       </c>
       <c r="D69" t="n">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>17.4%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp10.000.000</t>
+          <t>Rp11.200.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5885,16 +5885,16 @@
         <v>272</v>
       </c>
       <c r="D8" t="n">
-        <v>182</v>
+        <v>178</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>33.1%</t>
+          <t>34.6%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp40.900.000</t>
+          <t>Rp42.500.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -5947,16 +5947,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp7.675.000</t>
+          <t>Rp7.855.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6401,16 +6401,16 @@
         <v>74</v>
       </c>
       <c r="D4" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp11.790.000</t>
+          <t>Rp12.240.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>31.9%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp14.120.000</t>
+          <t>Rp14.300.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>122</v>
+        <v>127</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>15.3%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp7.625.000</t>
+          <t>Rp5.800.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp17.430.000</t>
+          <t>Rp18.006.500</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6835,16 +6835,16 @@
         <v>90</v>
       </c>
       <c r="D18" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp1.200.000</t>
+          <t>Rp1.350.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp6.370.000</t>
+          <t>Rp5.255.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>36</v>
       </c>
       <c r="D26" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.495.000</t>
+          <t>Rp1.585.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>108</v>
       </c>
       <c r="D32" t="n">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp6.845.000</t>
+          <t>Rp7.235.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>98</v>
       </c>
       <c r="D47" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>45.9%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp9.640.000</t>
+          <t>Rp9.790.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -8064,16 +8064,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.295.000</t>
+          <t>Rp1.445.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp4.690.000</t>
+          <t>Rp4.225.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>36</v>
       </c>
       <c r="D25" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.724.000</t>
+          <t>Rp2.994.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp5.210.000</t>
+          <t>Rp5.425.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp3.569.000</t>
+          <t>Rp3.619.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp4.930.000</t>
+          <t>Rp4.630.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>68</v>
       </c>
       <c r="D42" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp995.000</t>
+          <t>Rp1.791.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-18.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-18.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.600.000</t>
+          <t>Rp1.680.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -544,16 +544,16 @@
         <v>144</v>
       </c>
       <c r="D4" t="n">
-        <v>127</v>
+        <v>121</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp11.260.000</t>
+          <t>Rp12.550.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>64</v>
+        <v>57</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp2.584.000</t>
+          <t>Rp3.277.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp6.960.000</t>
+          <t>Rp8.060.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -699,16 +699,16 @@
         <v>68</v>
       </c>
       <c r="D9" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp6.375.000</t>
+          <t>Rp7.025.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.057.987</t>
+          <t>Rp6.395.987</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -761,16 +761,16 @@
         <v>126</v>
       </c>
       <c r="D11" t="n">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>23.8%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp6.400.000</t>
+          <t>Rp6.525.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp5.720.000</t>
+          <t>Rp7.850.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1009,16 +1009,16 @@
         <v>48</v>
       </c>
       <c r="D19" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.338.000</t>
+          <t>Rp1.776.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>127</v>
       </c>
       <c r="D20" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp15.300.000</t>
+          <t>Rp15.700.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>102</v>
       </c>
       <c r="D22" t="n">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>13.7%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp2.600.000</t>
+          <t>Rp3.150.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>72</v>
       </c>
       <c r="D24" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp5.200.000</t>
+          <t>Rp5.325.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1226,16 +1226,16 @@
         <v>16</v>
       </c>
       <c r="D26" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp850.000</t>
+          <t>Rp975.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1319,16 +1319,16 @@
         <v>54</v>
       </c>
       <c r="D29" t="n">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp1.640.000</t>
+          <t>Rp2.120.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>85</v>
       </c>
       <c r="D31" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.222.000</t>
+          <t>Rp3.418.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>72</v>
       </c>
       <c r="D33" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp2.876.000</t>
+          <t>Rp3.122.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp6.800.000</t>
+          <t>Rp6.990.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>198</v>
       </c>
       <c r="D42" t="n">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.825.000</t>
+          <t>Rp3.425.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1939,16 +1939,16 @@
         <v>84</v>
       </c>
       <c r="D49" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>20.2%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Rp6.133.000</t>
+          <t>Rp6.683.000</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -2156,16 +2156,16 @@
         <v>54</v>
       </c>
       <c r="D56" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp685.000</t>
+          <t>Rp845.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>144</v>
       </c>
       <c r="D59" t="n">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp2.293.000</t>
+          <t>Rp1.894.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2435,16 +2435,16 @@
         <v>90</v>
       </c>
       <c r="D65" t="n">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp6.848.000</t>
+          <t>Rp6.051.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>96</v>
       </c>
       <c r="D73" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp4.200.000</t>
+          <t>Rp3.855.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2714,16 +2714,16 @@
         <v>112</v>
       </c>
       <c r="D74" t="n">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Rp1.900.000</t>
+          <t>Rp3.100.000</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>108</v>
       </c>
       <c r="D76" t="n">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp3.825.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>80</v>
       </c>
       <c r="D78" t="n">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>21.2%</t>
+          <t>26.2%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp3.000.000</t>
+          <t>Rp3.750.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2931,16 +2931,16 @@
         <v>14</v>
       </c>
       <c r="D81" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Rp900.000</t>
+          <t>Rp1.175.000</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -3024,16 +3024,16 @@
         <v>36</v>
       </c>
       <c r="D84" t="n">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp2.280.000</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3117,16 +3117,16 @@
         <v>90</v>
       </c>
       <c r="D87" t="n">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rp4.000.000</t>
+          <t>Rp4.550.000</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3241,16 +3241,16 @@
         <v>36</v>
       </c>
       <c r="D91" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>30.6%</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rp1.368.000</t>
+          <t>Rp1.229.000</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -3303,16 +3303,16 @@
         <v>64</v>
       </c>
       <c r="D93" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>14.1%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rp1.980.000</t>
+          <t>Rp2.230.000</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -3334,16 +3334,16 @@
         <v>112</v>
       </c>
       <c r="D94" t="n">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rp2.890.000</t>
+          <t>Rp3.210.000</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3664,16 +3664,16 @@
         <v>36</v>
       </c>
       <c r="D8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp3.100.000</t>
+          <t>Rp3.400.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3850,16 +3850,16 @@
         <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp6.575.000</t>
+          <t>Rp6.800.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -3974,16 +3974,16 @@
         <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp7.695.000</t>
+          <t>Rp8.505.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp4.650.000</t>
+          <t>Rp5.775.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4129,16 +4129,16 @@
         <v>34</v>
       </c>
       <c r="D23" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp2.460.000</t>
+          <t>Rp2.070.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4191,16 +4191,16 @@
         <v>53</v>
       </c>
       <c r="D25" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp11.250.000</t>
+          <t>Rp11.950.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -4222,16 +4222,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.310.000</t>
+          <t>Rp1.945.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -4253,16 +4253,16 @@
         <v>17</v>
       </c>
       <c r="D27" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>0.0%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp80.000</t>
+          <t>Rp0</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -4532,16 +4532,16 @@
         <v>70</v>
       </c>
       <c r="D36" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>21.4%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rp3.500.000</t>
+          <t>Rp3.100.000</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -4594,16 +4594,16 @@
         <v>159</v>
       </c>
       <c r="D38" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp26.000.000</t>
+          <t>Rp26.300.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>52</v>
       </c>
       <c r="D43" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>36.5%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp6.297.000</t>
+          <t>Rp6.897.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4904,16 +4904,16 @@
         <v>14</v>
       </c>
       <c r="D48" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>14.3%</t>
+          <t>21.4%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp650.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -4997,16 +4997,16 @@
         <v>80</v>
       </c>
       <c r="D51" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rp6.375.000</t>
+          <t>Rp5.875.000</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -5059,16 +5059,16 @@
         <v>72</v>
       </c>
       <c r="D53" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp3.960.000</t>
+          <t>Rp4.560.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -5214,16 +5214,16 @@
         <v>126</v>
       </c>
       <c r="D58" t="n">
-        <v>102</v>
+        <v>106</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>15.9%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rp7.850.000</t>
+          <t>Rp6.400.000</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>70</v>
       </c>
       <c r="D59" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp159.000</t>
+          <t>Rp230.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5493,16 +5493,16 @@
         <v>102</v>
       </c>
       <c r="D67" t="n">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Rp7.272.000</t>
+          <t>Rp8.163.000</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>144</v>
       </c>
       <c r="D69" t="n">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp11.200.000</t>
+          <t>Rp12.700.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5586,16 +5586,16 @@
         <v>30</v>
       </c>
       <c r="D70" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>60.0%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp2.250.000</t>
+          <t>Rp2.550.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -5699,16 +5699,16 @@
         <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp420.000</t>
+          <t>Rp740.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -5792,16 +5792,16 @@
         <v>108</v>
       </c>
       <c r="D5" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp15.000.000</t>
+          <t>Rp15.700.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5823,16 +5823,16 @@
         <v>36</v>
       </c>
       <c r="D6" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp2.040.000</t>
+          <t>Rp2.300.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -5854,16 +5854,16 @@
         <v>68</v>
       </c>
       <c r="D7" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp2.050.000</t>
+          <t>Rp2.450.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -5885,16 +5885,16 @@
         <v>272</v>
       </c>
       <c r="D8" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>34.6%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp42.500.000</t>
+          <t>Rp41.300.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -5916,16 +5916,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp5.275.000</t>
+          <t>Rp6.025.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>85</v>
       </c>
       <c r="D16" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>28.2%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp9.075.000</t>
+          <t>Rp9.625.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6339,16 +6339,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>22.0%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp13.260.000</t>
+          <t>Rp13.510.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6370,16 +6370,16 @@
         <v>86</v>
       </c>
       <c r="D3" t="n">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>17.4%</t>
+          <t>22.1%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp5.700.000</t>
+          <t>Rp6.160.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6432,16 +6432,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp504.000</t>
+          <t>Rp642.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6587,16 +6587,16 @@
         <v>60</v>
       </c>
       <c r="D10" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp2.300.000</t>
+          <t>Rp2.050.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp1.800.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp7.680.000</t>
+          <t>Rp8.355.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6742,16 +6742,16 @@
         <v>102</v>
       </c>
       <c r="D15" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp5.100.000</t>
+          <t>Rp5.300.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>108</v>
       </c>
       <c r="D25" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp8.210.000</t>
+          <t>Rp8.485.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>36</v>
       </c>
       <c r="D26" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.585.000</t>
+          <t>Rp1.685.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>108</v>
       </c>
       <c r="D32" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp7.235.000</t>
+          <t>Rp7.625.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7309,12 +7309,12 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp27.900.000</t>
+          <t>Rp27.650.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Rp200.000 - Rp500.000</t>
+          <t>Rp75.000 - Rp500.000</t>
         </is>
       </c>
     </row>
@@ -7331,16 +7331,16 @@
         <v>67</v>
       </c>
       <c r="D34" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>40.3%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp6.200.000</t>
+          <t>Rp6.776.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>150</v>
       </c>
       <c r="D39" t="n">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>46.0%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp20.275.000</t>
+          <t>Rp22.975.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>56</v>
       </c>
       <c r="D41" t="n">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>174</v>
       </c>
       <c r="D43" t="n">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>40.2%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp37.800.000</t>
+          <t>Rp39.800.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -7703,16 +7703,16 @@
         <v>108</v>
       </c>
       <c r="D46" t="n">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp1.650.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>98</v>
       </c>
       <c r="D47" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>45.9%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp9.790.000</t>
+          <t>Rp10.130.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -8126,16 +8126,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp7.890.000</t>
+          <t>Rp8.040.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8157,16 +8157,16 @@
         <v>108</v>
       </c>
       <c r="D11" t="n">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp5.055.000</t>
+          <t>Rp6.275.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp9.958.500</t>
+          <t>Rp10.228.500</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>64.7%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp5.375.000</t>
+          <t>Rp5.500.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp3.100.000</t>
+          <t>Rp2.925.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8467,16 +8467,16 @@
         <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>49.1%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp19.820.000</t>
+          <t>Rp21.640.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>68.5%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp5.975.000</t>
+          <t>Rp6.100.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp5.425.000</t>
+          <t>Rp5.995.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp2.700.000</t>
+          <t>Rp3.200.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8746,16 +8746,16 @@
         <v>32</v>
       </c>
       <c r="D30" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>71.9%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp2.825.000</t>
+          <t>Rp3.075.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>54</v>
       </c>
       <c r="D31" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>40.7%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.900.000</t>
+          <t>Rp4.125.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -8870,16 +8870,16 @@
         <v>54</v>
       </c>
       <c r="D34" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp2.140.000</t>
+          <t>Rp2.510.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -8963,16 +8963,16 @@
         <v>51</v>
       </c>
       <c r="D37" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>17.6%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp1.665.000</t>
+          <t>Rp1.480.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>58.3%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp3.619.000</t>
+          <t>Rp4.016.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp4.630.000</t>
+          <t>Rp4.330.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-18.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-18.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>21.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.680.000</t>
+          <t>Rp1.840.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -513,16 +513,16 @@
         <v>68</v>
       </c>
       <c r="D3" t="n">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp3.698.000</t>
+          <t>Rp3.323.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -544,16 +544,16 @@
         <v>144</v>
       </c>
       <c r="D4" t="n">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp12.550.000</t>
+          <t>Rp13.750.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -575,16 +575,16 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp3.277.000</t>
+          <t>Rp2.978.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp8.060.000</t>
+          <t>Rp9.435.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.395.987</t>
+          <t>Rp6.744.986</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -792,16 +792,16 @@
         <v>96</v>
       </c>
       <c r="D12" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>27.1%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp7.850.000</t>
+          <t>Rp6.350.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -823,16 +823,16 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp4.600.000</t>
+          <t>Rp5.100.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -854,16 +854,16 @@
         <v>180</v>
       </c>
       <c r="D14" t="n">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>26.1%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp10.172.000</t>
+          <t>Rp10.758.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -916,16 +916,16 @@
         <v>144</v>
       </c>
       <c r="D16" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp640.000</t>
+          <t>Rp1.440.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -947,16 +947,16 @@
         <v>72</v>
       </c>
       <c r="D17" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp2.800.000</t>
+          <t>Rp3.000.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>102</v>
       </c>
       <c r="D22" t="n">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp3.150.000</t>
+          <t>Rp4.500.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1133,16 +1133,16 @@
         <v>144</v>
       </c>
       <c r="D23" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp5.600.000</t>
+          <t>Rp6.000.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>72</v>
       </c>
       <c r="D24" t="n">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp5.325.000</t>
+          <t>Rp5.950.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>51</v>
       </c>
       <c r="D25" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp975.000</t>
+          <t>Rp1.575.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1257,16 +1257,16 @@
         <v>36</v>
       </c>
       <c r="D27" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>0.0%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp0</t>
+          <t>Rp796.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -1381,16 +1381,16 @@
         <v>85</v>
       </c>
       <c r="D31" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>24.7%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp3.418.000</t>
+          <t>Rp3.818.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>72</v>
       </c>
       <c r="D33" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.122.000</t>
+          <t>Rp3.368.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1598,16 +1598,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp1.260.000</t>
+          <t>Rp1.680.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -1629,16 +1629,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp1.519.000</t>
+          <t>Rp2.593.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -1660,16 +1660,16 @@
         <v>51</v>
       </c>
       <c r="D40" t="n">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>25.5%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.925.000</t>
+          <t>Rp2.255.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -1691,16 +1691,16 @@
         <v>180</v>
       </c>
       <c r="D41" t="n">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>18.9%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp10.400.000</t>
+          <t>Rp10.050.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>198</v>
       </c>
       <c r="D42" t="n">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp3.425.000</t>
+          <t>Rp3.725.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1846,16 +1846,16 @@
         <v>96</v>
       </c>
       <c r="D46" t="n">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Rp4.813.000</t>
+          <t>Rp4.912.000</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -1877,16 +1877,16 @@
         <v>105</v>
       </c>
       <c r="D47" t="n">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp6.445.000</t>
+          <t>Rp5.155.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -2032,16 +2032,16 @@
         <v>60</v>
       </c>
       <c r="D52" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp592.000</t>
+          <t>Rp700.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -2063,16 +2063,16 @@
         <v>32</v>
       </c>
       <c r="D53" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rp800.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -2094,16 +2094,16 @@
         <v>18</v>
       </c>
       <c r="D54" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp1.094.000</t>
+          <t>Rp1.294.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -2125,16 +2125,16 @@
         <v>48</v>
       </c>
       <c r="D55" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.1%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp2.205.000</t>
+          <t>Rp2.320.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -2156,16 +2156,16 @@
         <v>54</v>
       </c>
       <c r="D56" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rp845.000</t>
+          <t>Rp925.000</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
@@ -2187,16 +2187,16 @@
         <v>32</v>
       </c>
       <c r="D57" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rp3.225.000</t>
+          <t>Rp3.500.000</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -2249,16 +2249,16 @@
         <v>144</v>
       </c>
       <c r="D59" t="n">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>14.6%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp1.894.000</t>
+          <t>Rp2.592.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -2280,16 +2280,16 @@
         <v>90</v>
       </c>
       <c r="D60" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rp6.100.000</t>
+          <t>Rp6.700.000</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>68</v>
       </c>
       <c r="D61" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>36.8%</t>
+          <t>39.7%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp4.010.000</t>
+          <t>Rp4.190.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2528,16 +2528,16 @@
         <v>176</v>
       </c>
       <c r="D68" t="n">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp3.237.000</t>
+          <t>Rp2.739.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>108</v>
       </c>
       <c r="D69" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp4.662.500</t>
+          <t>Rp4.262.500</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2590,16 +2590,16 @@
         <v>68</v>
       </c>
       <c r="D70" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Rp1.440.000</t>
+          <t>Rp1.800.000</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>72</v>
       </c>
       <c r="D71" t="n">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp1.375.000</t>
+          <t>Rp1.865.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2683,16 +2683,16 @@
         <v>96</v>
       </c>
       <c r="D73" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Rp3.855.000</t>
+          <t>Rp3.075.000</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -2745,16 +2745,16 @@
         <v>120</v>
       </c>
       <c r="D75" t="n">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>21.7%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Rp4.500.000</t>
+          <t>Rp4.680.000</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>80</v>
       </c>
       <c r="D78" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>26.2%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp4.450.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -2962,16 +2962,16 @@
         <v>135</v>
       </c>
       <c r="D82" t="n">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>138</v>
       </c>
       <c r="D86" t="n">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>29.7%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp7.300.000</t>
+          <t>Rp7.400.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3117,16 +3117,16 @@
         <v>90</v>
       </c>
       <c r="D87" t="n">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rp4.550.000</t>
+          <t>Rp4.150.000</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3210,16 +3210,16 @@
         <v>28</v>
       </c>
       <c r="D90" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rp1.089.000</t>
+          <t>Rp792.000</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -3272,16 +3272,16 @@
         <v>34</v>
       </c>
       <c r="D92" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rp2.150.000</t>
+          <t>Rp2.375.000</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -3334,16 +3334,16 @@
         <v>112</v>
       </c>
       <c r="D94" t="n">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rp3.210.000</t>
+          <t>Rp4.110.000</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -3509,16 +3509,16 @@
         <v>119</v>
       </c>
       <c r="D3" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>61.3%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp18.415.948</t>
+          <t>Rp18.735.950</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -3540,16 +3540,16 @@
         <v>102</v>
       </c>
       <c r="D4" t="n">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>19.6%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp5.834.000</t>
+          <t>Rp7.390.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>96</v>
       </c>
       <c r="D5" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp12.300.000</t>
+          <t>Rp13.000.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3726,16 +3726,16 @@
         <v>144</v>
       </c>
       <c r="D10" t="n">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>7.6%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp741.000</t>
+          <t>Rp1.091.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -3788,16 +3788,16 @@
         <v>15</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp1.020.000</t>
+          <t>Rp770.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -3819,16 +3819,16 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp4.020.000</t>
+          <t>Rp4.415.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -3974,16 +3974,16 @@
         <v>65</v>
       </c>
       <c r="D18" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp8.505.000</t>
+          <t>Rp9.720.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -4005,16 +4005,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp5.775.000</t>
+          <t>Rp6.500.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>36</v>
       </c>
       <c r="D20" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp750.000</t>
+          <t>Rp1.000.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -4129,16 +4129,16 @@
         <v>34</v>
       </c>
       <c r="D23" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>38.2%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp2.070.000</t>
+          <t>Rp2.265.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -4222,16 +4222,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>14.8%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.945.000</t>
+          <t>Rp2.330.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -4284,16 +4284,16 @@
         <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp8.469.000</t>
+          <t>Rp8.768.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -4315,16 +4315,16 @@
         <v>180</v>
       </c>
       <c r="D29" t="n">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp19.470.000</t>
+          <t>Rp20.895.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4346,16 +4346,16 @@
         <v>36</v>
       </c>
       <c r="D30" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rp3.600.000</t>
+          <t>Rp3.925.000</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -4377,16 +4377,16 @@
         <v>32</v>
       </c>
       <c r="D31" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp2.400.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -4718,16 +4718,16 @@
         <v>54</v>
       </c>
       <c r="D42" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp2.150.000</t>
+          <t>Rp2.535.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -4749,16 +4749,16 @@
         <v>52</v>
       </c>
       <c r="D43" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>44.2%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp6.897.000</t>
+          <t>Rp7.497.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -4780,16 +4780,16 @@
         <v>64</v>
       </c>
       <c r="D44" t="n">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>17.2%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp2.800.000</t>
+          <t>Rp2.200.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -4811,16 +4811,16 @@
         <v>64</v>
       </c>
       <c r="D45" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>7.8%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp1.250.000</t>
+          <t>Rp2.250.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -5028,16 +5028,16 @@
         <v>90</v>
       </c>
       <c r="D52" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -5090,16 +5090,16 @@
         <v>54</v>
       </c>
       <c r="D54" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rp8.750.000</t>
+          <t>Rp7.550.000</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -5121,16 +5121,16 @@
         <v>60</v>
       </c>
       <c r="D55" t="n">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rp4.500.000</t>
+          <t>Rp5.550.000</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>70</v>
       </c>
       <c r="D59" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp230.000</t>
+          <t>Rp416.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5409,12 +5409,12 @@
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rp4.300.000</t>
+          <t>Rp3.460.000</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Rp350.000 - Rp400.000</t>
+          <t>Rp175.000 - Rp400.000</t>
         </is>
       </c>
     </row>
@@ -5431,16 +5431,16 @@
         <v>64</v>
       </c>
       <c r="D65" t="n">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>20.3%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp7.800.000</t>
+          <t>Rp9.000.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -5524,16 +5524,16 @@
         <v>72</v>
       </c>
       <c r="D68" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp8.485.000</t>
+          <t>Rp8.135.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5555,16 +5555,16 @@
         <v>144</v>
       </c>
       <c r="D69" t="n">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>20.1%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp12.700.000</t>
+          <t>Rp13.250.000</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5730,16 +5730,16 @@
         <v>324</v>
       </c>
       <c r="D3" t="n">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp19.470.000</t>
+          <t>Rp23.540.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -5792,16 +5792,16 @@
         <v>108</v>
       </c>
       <c r="D5" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp15.700.000</t>
+          <t>Rp16.050.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5854,16 +5854,16 @@
         <v>68</v>
       </c>
       <c r="D7" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp2.450.000</t>
+          <t>Rp2.350.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -5885,16 +5885,16 @@
         <v>272</v>
       </c>
       <c r="D8" t="n">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp41.300.000</t>
+          <t>Rp42.750.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -5978,16 +5978,16 @@
         <v>36</v>
       </c>
       <c r="D11" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp2.543.000</t>
+          <t>Rp2.967.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6130,14 +6130,14 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="D16" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>28.2%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -6339,16 +6339,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>145</v>
+        <v>142</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>22.0%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp13.510.000</t>
+          <t>Rp14.510.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6370,16 +6370,16 @@
         <v>86</v>
       </c>
       <c r="D3" t="n">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>22.1%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp6.160.000</t>
+          <t>Rp6.670.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6432,16 +6432,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp642.000</t>
+          <t>Rp1.147.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp3.250.000</t>
+          <t>Rp4.025.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6618,16 +6618,16 @@
         <v>216</v>
       </c>
       <c r="D11" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp18.006.500</t>
+          <t>Rp18.286.500</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -6680,16 +6680,16 @@
         <v>42</v>
       </c>
       <c r="D13" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp1.914.000</t>
+          <t>Rp3.110.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -6711,16 +6711,16 @@
         <v>144</v>
       </c>
       <c r="D14" t="n">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>23.6%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp8.355.000</t>
+          <t>Rp9.365.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6897,16 +6897,16 @@
         <v>56</v>
       </c>
       <c r="D20" t="n">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>26.8%</t>
+          <t>28.6%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp1.485.000</t>
+          <t>Rp1.584.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>40.5%</t>
+          <t>42.5%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp20.600.000</t>
+          <t>Rp21.400.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>28.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp5.255.000</t>
+          <t>Rp4.059.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>108</v>
       </c>
       <c r="D25" t="n">
-        <v>73</v>
+        <v>68</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp8.485.000</t>
+          <t>Rp9.860.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7083,16 +7083,16 @@
         <v>36</v>
       </c>
       <c r="D26" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp1.685.000</t>
+          <t>Rp1.510.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>19.8%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp6.750.000</t>
+          <t>Rp3.750.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7145,16 +7145,16 @@
         <v>68</v>
       </c>
       <c r="D28" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>14.7%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp2.160.000</t>
+          <t>Rp2.850.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>108</v>
       </c>
       <c r="D32" t="n">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp7.625.000</t>
+          <t>Rp8.360.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7309,7 +7309,7 @@
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp27.650.000</t>
+          <t>Rp23.450.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>67</v>
       </c>
       <c r="D34" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>40.3%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp6.776.000</t>
+          <t>Rp7.352.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>102</v>
       </c>
       <c r="D35" t="n">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp4.275.000</t>
+          <t>Rp4.845.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7486,16 +7486,16 @@
         <v>150</v>
       </c>
       <c r="D39" t="n">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp22.975.000</t>
+          <t>Rp23.675.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -7517,16 +7517,16 @@
         <v>112</v>
       </c>
       <c r="D40" t="n">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>27.7%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp11.999.000</t>
+          <t>Rp11.199.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -7548,16 +7548,16 @@
         <v>56</v>
       </c>
       <c r="D41" t="n">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>19.6%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rp2.200.000</t>
+          <t>Rp2.800.000</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>98</v>
       </c>
       <c r="D47" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>49.0%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp10.130.000</t>
+          <t>Rp10.820.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>144</v>
       </c>
       <c r="D48" t="n">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp5.720.000</t>
+          <t>Rp6.040.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -7878,16 +7878,16 @@
         <v>72</v>
       </c>
       <c r="D2" t="n">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -7909,16 +7909,16 @@
         <v>136</v>
       </c>
       <c r="D3" t="n">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>55.1%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp13.375.000</t>
+          <t>Rp13.985.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -7940,16 +7940,16 @@
         <v>34</v>
       </c>
       <c r="D4" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>14.7%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp1.280.000</t>
+          <t>Rp2.060.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -7971,16 +7971,16 @@
         <v>88</v>
       </c>
       <c r="D5" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>31.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp7.450.000</t>
+          <t>Rp8.500.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8126,16 +8126,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp8.040.000</t>
+          <t>Rp7.785.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8157,16 +8157,16 @@
         <v>108</v>
       </c>
       <c r="D11" t="n">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>19.4%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rp6.275.000</t>
+          <t>Rp7.445.000</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -8188,16 +8188,16 @@
         <v>72</v>
       </c>
       <c r="D12" t="n">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp10.228.500</t>
+          <t>Rp9.148.500</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8219,16 +8219,16 @@
         <v>26</v>
       </c>
       <c r="D13" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp1.300.000</t>
+          <t>Rp1.400.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -8281,16 +8281,16 @@
         <v>51</v>
       </c>
       <c r="D15" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>64.7%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp5.500.000</t>
+          <t>Rp5.750.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -8312,16 +8312,16 @@
         <v>72</v>
       </c>
       <c r="D16" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp2.925.000</t>
+          <t>Rp3.425.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.179.000</t>
+          <t>Rp1.449.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8405,16 +8405,16 @@
         <v>54</v>
       </c>
       <c r="D19" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rp1.330.000</t>
+          <t>Rp2.280.000</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp4.225.000</t>
+          <t>Rp5.420.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8467,16 +8467,16 @@
         <v>108</v>
       </c>
       <c r="D21" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp21.640.000</t>
+          <t>Rp22.600.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -8529,16 +8529,16 @@
         <v>64</v>
       </c>
       <c r="D23" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>20.3%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp3.780.000</t>
+          <t>Rp4.095.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -8560,16 +8560,16 @@
         <v>144</v>
       </c>
       <c r="D24" t="n">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp4.395.000</t>
+          <t>Rp4.980.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -8591,16 +8591,16 @@
         <v>36</v>
       </c>
       <c r="D25" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp2.994.000</t>
+          <t>Rp3.193.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>64.8%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp6.100.000</t>
+          <t>Rp5.275.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp5.995.000</t>
+          <t>Rp5.425.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -8684,16 +8684,16 @@
         <v>32</v>
       </c>
       <c r="D28" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>40.6%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp1.785.000</t>
+          <t>Rp1.930.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp3.200.000</t>
+          <t>Rp2.950.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8808,16 +8808,16 @@
         <v>54</v>
       </c>
       <c r="D32" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp2.820.000</t>
+          <t>Rp3.365.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -8839,16 +8839,16 @@
         <v>34</v>
       </c>
       <c r="D33" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>35.3%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.055.000</t>
+          <t>Rp3.305.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -8901,16 +8901,16 @@
         <v>36</v>
       </c>
       <c r="D35" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp3.550.000</t>
+          <t>Rp3.785.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp4.330.000</t>
+          <t>Rp3.580.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-18.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-18.xlsx
@@ -544,16 +544,16 @@
         <v>144</v>
       </c>
       <c r="D4" t="n">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>21.5%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp13.750.000</t>
+          <t>Rp14.950.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -668,16 +668,16 @@
         <v>64</v>
       </c>
       <c r="D8" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp9.435.000</t>
+          <t>Rp9.985.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1040,16 +1040,16 @@
         <v>127</v>
       </c>
       <c r="D20" t="n">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp15.700.000</t>
+          <t>Rp16.190.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1102,16 +1102,16 @@
         <v>102</v>
       </c>
       <c r="D22" t="n">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rp4.500.000</t>
+          <t>Rp5.300.000</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>72</v>
       </c>
       <c r="D24" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>47.2%</t>
+          <t>48.6%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp5.950.000</t>
+          <t>Rp6.245.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1195,16 +1195,16 @@
         <v>51</v>
       </c>
       <c r="D25" t="n">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp1.575.000</t>
+          <t>Rp1.125.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1319,16 +1319,16 @@
         <v>54</v>
       </c>
       <c r="D29" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>20.4%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp2.120.000</t>
+          <t>Rp2.600.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -1412,16 +1412,16 @@
         <v>68</v>
       </c>
       <c r="D32" t="n">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp3.845.000</t>
+          <t>Rp4.075.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -1443,16 +1443,16 @@
         <v>72</v>
       </c>
       <c r="D33" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rp3.368.000</t>
+          <t>Rp3.516.000</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp6.990.000</t>
+          <t>Rp7.370.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -1567,16 +1567,16 @@
         <v>32</v>
       </c>
       <c r="D37" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rp1.400.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
@@ -1722,16 +1722,16 @@
         <v>198</v>
       </c>
       <c r="D42" t="n">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>12.6%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp3.725.000</t>
+          <t>Rp4.175.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -1784,16 +1784,16 @@
         <v>45</v>
       </c>
       <c r="D44" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp2.225.000</t>
+          <t>Rp1.875.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -1815,16 +1815,16 @@
         <v>54</v>
       </c>
       <c r="D45" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp2.220.000</t>
+          <t>Rp2.320.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -1970,16 +1970,16 @@
         <v>64</v>
       </c>
       <c r="D50" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rp8.640.000</t>
+          <t>Rp8.928.000</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>108</v>
       </c>
       <c r="D69" t="n">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp4.262.500</t>
+          <t>Rp5.362.500</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>72</v>
       </c>
       <c r="D71" t="n">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>25.0%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp1.865.000</t>
+          <t>Rp2.015.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2838,16 +2838,16 @@
         <v>80</v>
       </c>
       <c r="D78" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>31.2%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Rp4.450.000</t>
+          <t>Rp4.650.000</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -3024,16 +3024,16 @@
         <v>36</v>
       </c>
       <c r="D84" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>19.4%</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Rp2.280.000</t>
+          <t>Rp2.660.000</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
@@ -3086,16 +3086,16 @@
         <v>138</v>
       </c>
       <c r="D86" t="n">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>29.7%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Rp7.400.000</t>
+          <t>Rp7.600.000</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
@@ -3117,16 +3117,16 @@
         <v>90</v>
       </c>
       <c r="D87" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Rp4.150.000</t>
+          <t>Rp3.750.000</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
@@ -3633,16 +3633,16 @@
         <v>162</v>
       </c>
       <c r="D7" t="n">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp7.370.000</t>
+          <t>Rp7.720.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -4036,16 +4036,16 @@
         <v>36</v>
       </c>
       <c r="D20" t="n">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp1.000.000</t>
+          <t>Rp1.250.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -4222,16 +4222,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>18.5%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp2.330.000</t>
+          <t>Rp3.100.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -4284,16 +4284,16 @@
         <v>64</v>
       </c>
       <c r="D28" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>50.0%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rp8.768.000</t>
+          <t>Rp9.366.000</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -5245,16 +5245,16 @@
         <v>70</v>
       </c>
       <c r="D59" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rp416.000</t>
+          <t>Rp540.000</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5761,16 +5761,16 @@
         <v>30</v>
       </c>
       <c r="D4" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>40.0%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rp2.025.000</t>
+          <t>Rp2.150.000</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -6432,16 +6432,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp1.147.000</t>
+          <t>Rp1.246.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6494,16 +6494,16 @@
         <v>144</v>
       </c>
       <c r="D7" t="n">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp5.800.000</t>
+          <t>Rp6.500.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -6773,16 +6773,16 @@
         <v>108</v>
       </c>
       <c r="D16" t="n">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp6.175.000</t>
+          <t>Rp6.450.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp6.990.000</t>
+          <t>Rp7.166.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6928,16 +6928,16 @@
         <v>153</v>
       </c>
       <c r="D21" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rp21.400.000</t>
+          <t>Rp21.700.000</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>25.9%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.059.000</t>
+          <t>Rp4.358.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7052,16 +7052,16 @@
         <v>108</v>
       </c>
       <c r="D25" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>38.9%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rp9.860.000</t>
+          <t>Rp10.334.000</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -7269,16 +7269,16 @@
         <v>108</v>
       </c>
       <c r="D32" t="n">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rp8.360.000</t>
+          <t>Rp8.850.000</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
@@ -7331,16 +7331,16 @@
         <v>67</v>
       </c>
       <c r="D34" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp7.352.000</t>
+          <t>Rp7.928.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>102</v>
       </c>
       <c r="D35" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>15.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp4.845.000</t>
+          <t>Rp4.560.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7610,16 +7610,16 @@
         <v>174</v>
       </c>
       <c r="D43" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>42.5%</t>
+          <t>43.1%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rp39.800.000</t>
+          <t>Rp40.400.000</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
@@ -7765,16 +7765,16 @@
         <v>144</v>
       </c>
       <c r="D48" t="n">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Rp6.040.000</t>
+          <t>Rp6.360.000</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -8002,16 +8002,16 @@
         <v>72</v>
       </c>
       <c r="D6" t="n">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp5.580.000</t>
+          <t>Rp6.576.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -8436,16 +8436,16 @@
         <v>48</v>
       </c>
       <c r="D20" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Rp5.420.000</t>
+          <t>Rp5.760.000</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8622,16 +8622,16 @@
         <v>54</v>
       </c>
       <c r="D26" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>64.8%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rp5.275.000</t>
+          <t>Rp4.725.000</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -8715,16 +8715,16 @@
         <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp2.950.000</t>
+          <t>Rp2.700.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -8777,16 +8777,16 @@
         <v>54</v>
       </c>
       <c r="D31" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rp4.125.000</t>
+          <t>Rp4.575.000</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -8994,16 +8994,16 @@
         <v>72</v>
       </c>
       <c r="D38" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp4.016.000</t>
+          <t>Rp4.115.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>37.0%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp3.580.000</t>
+          <t>Rp4.080.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
@@ -9056,16 +9056,16 @@
         <v>64</v>
       </c>
       <c r="D40" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Rp1.352.000</t>
+          <t>Rp1.521.000</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -9118,16 +9118,16 @@
         <v>68</v>
       </c>
       <c r="D42" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rp1.791.000</t>
+          <t>Rp2.189.000</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">

--- a/laporan_padel_dki_jakarta_2026-09-18.xlsx
+++ b/laporan_padel_dki_jakarta_2026-09-18.xlsx
@@ -482,16 +482,16 @@
         <v>108</v>
       </c>
       <c r="D2" t="n">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>21.3%</t>
+          <t>23.1%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp1.840.000</t>
+          <t>Rp2.000.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -730,16 +730,16 @@
         <v>72</v>
       </c>
       <c r="D10" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>31.9%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp6.744.986</t>
+          <t>Rp6.406.986</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -823,16 +823,16 @@
         <v>51</v>
       </c>
       <c r="D13" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>43.1%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Rp5.100.000</t>
+          <t>Rp5.400.000</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -885,16 +885,16 @@
         <v>90</v>
       </c>
       <c r="D15" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rp2.425.000</t>
+          <t>Rp2.575.000</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -978,16 +978,16 @@
         <v>108</v>
       </c>
       <c r="D18" t="n">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp2.935.000</t>
+          <t>Rp3.935.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1164,16 +1164,16 @@
         <v>72</v>
       </c>
       <c r="D24" t="n">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>48.6%</t>
+          <t>45.8%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Rp6.245.000</t>
+          <t>Rp5.995.000</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1505,16 +1505,16 @@
         <v>72</v>
       </c>
       <c r="D35" t="n">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp7.370.000</t>
+          <t>Rp6.870.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -2311,16 +2311,16 @@
         <v>68</v>
       </c>
       <c r="D61" t="n">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>39.7%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rp4.190.000</t>
+          <t>Rp4.350.000</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
@@ -2435,16 +2435,16 @@
         <v>90</v>
       </c>
       <c r="D65" t="n">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>24.4%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rp6.051.000</t>
+          <t>Rp5.852.000</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
@@ -2559,16 +2559,16 @@
         <v>108</v>
       </c>
       <c r="D69" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Rp5.362.500</t>
+          <t>Rp5.562.500</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -2621,16 +2621,16 @@
         <v>72</v>
       </c>
       <c r="D71" t="n">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>25.0%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Rp2.015.000</t>
+          <t>Rp2.165.000</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
@@ -2776,16 +2776,16 @@
         <v>108</v>
       </c>
       <c r="D76" t="n">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>30.6%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Rp3.825.000</t>
+          <t>Rp4.275.000</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -3571,16 +3571,16 @@
         <v>96</v>
       </c>
       <c r="D5" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp13.000.000</t>
+          <t>Rp13.350.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -3850,16 +3850,16 @@
         <v>48</v>
       </c>
       <c r="D14" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>45.8%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rp6.800.000</t>
+          <t>Rp7.000.000</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -4315,16 +4315,16 @@
         <v>180</v>
       </c>
       <c r="D29" t="n">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>41.1%</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rp20.895.000</t>
+          <t>Rp20.720.000</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -4470,16 +4470,16 @@
         <v>90</v>
       </c>
       <c r="D34" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>32.2%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Rp5.825.000</t>
+          <t>Rp6.025.000</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
@@ -4594,16 +4594,16 @@
         <v>159</v>
       </c>
       <c r="D38" t="n">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>49.1%</t>
+          <t>49.7%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rp26.300.000</t>
+          <t>Rp26.450.000</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
@@ -5524,16 +5524,16 @@
         <v>72</v>
       </c>
       <c r="D68" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>33.3%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Rp8.135.000</t>
+          <t>Rp8.665.000</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -5699,16 +5699,16 @@
         <v>18</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp740.000</t>
+          <t>Rp900.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -5792,16 +5792,16 @@
         <v>108</v>
       </c>
       <c r="D5" t="n">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>49.1%</t>
+          <t>50.9%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp16.050.000</t>
+          <t>Rp16.550.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -5854,16 +5854,16 @@
         <v>68</v>
       </c>
       <c r="D7" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rp2.350.000</t>
+          <t>Rp2.450.000</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -5916,16 +5916,16 @@
         <v>54</v>
       </c>
       <c r="D9" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp6.025.000</t>
+          <t>Rp6.425.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6133,16 +6133,16 @@
         <v>91</v>
       </c>
       <c r="D16" t="n">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>27.5%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Rp9.625.000</t>
+          <t>Rp9.900.000</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6339,16 +6339,16 @@
         <v>186</v>
       </c>
       <c r="D2" t="n">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>24.7%</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rp14.510.000</t>
+          <t>Rp14.670.000</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -6370,16 +6370,16 @@
         <v>86</v>
       </c>
       <c r="D3" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>26.7%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rp6.670.000</t>
+          <t>Rp7.050.000</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -6432,16 +6432,16 @@
         <v>90</v>
       </c>
       <c r="D5" t="n">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>17.8%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp1.246.000</t>
+          <t>Rp1.384.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -6463,16 +6463,16 @@
         <v>216</v>
       </c>
       <c r="D6" t="n">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>32.4%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rp14.300.000</t>
+          <t>Rp14.495.000</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -6525,16 +6525,16 @@
         <v>54</v>
       </c>
       <c r="D8" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp4.025.000</t>
+          <t>Rp4.200.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -6556,16 +6556,16 @@
         <v>108</v>
       </c>
       <c r="D9" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>36.1%</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rp8.170.000</t>
+          <t>Rp8.369.000</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -6649,16 +6649,16 @@
         <v>54</v>
       </c>
       <c r="D12" t="n">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>18.5%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp2.000.000</t>
+          <t>Rp2.400.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -6804,16 +6804,16 @@
         <v>144</v>
       </c>
       <c r="D17" t="n">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp7.166.000</t>
+          <t>Rp7.342.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -6990,16 +6990,16 @@
         <v>112</v>
       </c>
       <c r="D23" t="n">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>25.9%</t>
+          <t>26.8%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rp4.358.000</t>
+          <t>Rp4.558.000</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -7114,16 +7114,16 @@
         <v>96</v>
       </c>
       <c r="D27" t="n">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>19.8%</t>
+          <t>20.8%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp3.750.000</t>
+          <t>Rp4.000.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -7362,16 +7362,16 @@
         <v>102</v>
       </c>
       <c r="D35" t="n">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>16.7%</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rp4.560.000</t>
+          <t>Rp4.759.000</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
@@ -7641,16 +7641,16 @@
         <v>102</v>
       </c>
       <c r="D44" t="n">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>7.8%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Rp1.310.000</t>
+          <t>Rp1.760.000</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -7672,16 +7672,16 @@
         <v>36</v>
       </c>
       <c r="D45" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>58.3%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Rp6.560.000</t>
+          <t>Rp7.060.000</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -7734,16 +7734,16 @@
         <v>98</v>
       </c>
       <c r="D47" t="n">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>49.0%</t>
+          <t>52.0%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Rp10.820.000</t>
+          <t>Rp11.270.000</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -7971,16 +7971,16 @@
         <v>88</v>
       </c>
       <c r="D5" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>31.8%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rp8.500.000</t>
+          <t>Rp9.250.000</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -8064,16 +8064,16 @@
         <v>51</v>
       </c>
       <c r="D8" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>15.7%</t>
+          <t>17.6%</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rp1.445.000</t>
+          <t>Rp1.595.000</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -8126,16 +8126,16 @@
         <v>90</v>
       </c>
       <c r="D10" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>43.3%</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rp7.785.000</t>
+          <t>Rp7.635.000</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -8197,7 +8197,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Rp9.148.500</t>
+          <t>Rp9.162.000</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -8343,16 +8343,16 @@
         <v>54</v>
       </c>
       <c r="D17" t="n">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>20.4%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rp1.449.000</t>
+          <t>Rp1.719.000</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -8374,16 +8374,16 @@
         <v>54</v>
       </c>
       <c r="D18" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rp5.985.000</t>
+          <t>Rp6.285.000</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -8653,16 +8653,16 @@
         <v>54</v>
       </c>
       <c r="D27" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>40.7%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rp5.425.000</t>
+          <t>Rp5.640.000</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
@@ -9025,16 +9025,16 @@
         <v>54</v>
       </c>
       <c r="D39" t="n">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>37.0%</t>
+          <t>42.6%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rp4.080.000</t>
+          <t>Rp4.530.000</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
